--- a/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
@@ -126,10 +126,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -161,10 +161,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>

--- a/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
@@ -126,10 +126,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -161,10 +161,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -445,7 +445,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" xml:space="preserve">
       <c r="A2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="str">
         <v>スタートAI</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="3" ht="17" customHeight="1" xml:space="preserve">
       <c r="A3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="str">
         <v>Enjoy Tech!</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" xml:space="preserve">
       <c r="A4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" t="str">
         <v>タケルFXスクール</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="5" ht="23" customHeight="1" xml:space="preserve">
       <c r="A5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="str">
         <v>SEO HOUSE</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" xml:space="preserve">
       <c r="A6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="str">
         <v>無料PHPスクール</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="7" ht="19" customHeight="1" xml:space="preserve">
       <c r="A7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="str">
         <v>株式会社フィットクルー</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="8" ht="21" customHeight="1" xml:space="preserve">
       <c r="A8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="str">
         <v>ハーブピーリング教室</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="9" ht="27" customHeight="1" xml:space="preserve">
       <c r="A9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="str">
         <v>ラスタイルアカデミー</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="12" ht="19" customHeight="1" xml:space="preserve">
       <c r="A12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="str">
         <v>KADODE Academy</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="14" ht="17" customHeight="1" xml:space="preserve">
       <c r="A14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" t="str">
         <v>MoneyWith</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="15" ht="19" customHeight="1" xml:space="preserve">
       <c r="A15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" t="str">
         <v>オンライン英語塾OUTCOME</v>

--- a/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
@@ -126,10 +126,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -161,10 +161,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I51"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="6.83333333333333"/>
     <col min="2" max="2" customWidth="1" width="26.8333333333333"/>
@@ -414,7 +414,7 @@
     <col min="9" max="9" customWidth="1" width="24.8333333333333"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
+    <row r="1">
       <c r="A1" t="str">
         <v>反映</v>
       </c>
@@ -443,7 +443,7 @@
         <v>備考</v>
       </c>
     </row>
-    <row r="2" ht="21" customHeight="1" xml:space="preserve">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -455,6 +455,15 @@
       </c>
       <c r="D2" t="str">
         <v>https://startai.jp/html/salp/seminar/intro/</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
       </c>
       <c r="H2" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -495,8 +504,11 @@
 ・企業でDXやAI導入を担当している方
 </v>
       </c>
-    </row>
-    <row r="3" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -508,6 +520,15 @@
       </c>
       <c r="D3" t="str">
         <v>https://pam-inc.co.jp/enjoy-tech/</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
       </c>
       <c r="H3" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -528,8 +549,11 @@
 ・スキルアップのための転職を検討している20-30代
 ・エンジニア就活を検討している大学生</v>
       </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -541,6 +565,15 @@
       </c>
       <c r="D4" t="str">
         <v>https://www.fxschool.or.jp/LP/brs/</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
       </c>
       <c r="H4" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -571,8 +604,11 @@
 男女比　男4：女6
 FXを勉強して、自身でFXトレードによる経済的自由の獲得を目指している方</v>
       </c>
-    </row>
-    <row r="5" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -584,6 +620,15 @@
       </c>
       <c r="D5" t="str">
         <v>https://seo-house.jp/</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
       <c r="H5" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -612,8 +657,11 @@
 ・自社サイトやオウンドメディアの集客力を高めたい経営者、担当者
 </v>
       </c>
-    </row>
-    <row r="6" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -625,6 +673,15 @@
       </c>
       <c r="D6" t="str">
         <v>https://www.dt30.net/phpschool/</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
       </c>
       <c r="H6" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -666,8 +723,11 @@
 ・IT/Webエンジニアとして就職・転職したい人(事業キャッシュポイントが、人材(職業)紹介のため)
 </v>
       </c>
-    </row>
-    <row r="7" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -679,6 +739,15 @@
       </c>
       <c r="D7" t="str">
         <v>https://www.progym.jp/</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7" t="str" xml:space="preserve">
         <v xml:space="preserve">写真素材
@@ -828,8 +897,11 @@
 広告素材/テキスト：有
 </v>
       </c>
-    </row>
-    <row r="8" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -841,6 +913,15 @@
       </c>
       <c r="D8" t="str">
         <v>https://revi-herb-peeling.hp.peraichi.com/</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
       </c>
       <c r="H8" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -870,8 +951,11 @@
 副業をしたい主婦
 </v>
       </c>
-    </row>
-    <row r="9" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -883,6 +967,15 @@
       </c>
       <c r="D9" t="str">
         <v>https://www.last-style.com/academy/</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
       </c>
       <c r="H9" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -910,8 +1003,11 @@
 在職中の転職希望者
 </v>
       </c>
-    </row>
-    <row r="10" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -923,6 +1019,15 @@
       </c>
       <c r="D10" t="str">
         <v>https://academy.kadode-group.co.jp/</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
       </c>
       <c r="H10" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -939,8 +1044,11 @@
 【ターゲット層】
 実務未経験からエンジニア転職を目指す、20～30代。利用者の多くはリスキリング助成金を利用して受講中の方</v>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -952,6 +1060,15 @@
       </c>
       <c r="D11" t="str">
         <v>https://money-with.jp/lp-rent01/</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
       </c>
       <c r="H11" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -971,8 +1088,11 @@
 ３０代〜５０代女性 主婦層 キャリアウーマン
 </v>
       </c>
-    </row>
-    <row r="12" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -984,6 +1104,15 @@
       </c>
       <c r="D12" t="str">
         <v>https://outcome-online.com/</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
       </c>
       <c r="H12" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -1010,8 +1139,11 @@
 【ターゲット層】
 中３、高１、高２の生徒とその保護者</v>
       </c>
-    </row>
-    <row r="13" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -1023,6 +1155,15 @@
       </c>
       <c r="D13" t="str">
         <v>https://www.alpros.co.jp/</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
       </c>
       <c r="H13" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -1061,8 +1202,11 @@
 ・英語初心者～上級者、特に中級レベルから脱せず伸び悩んでる方
 </v>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
       <c r="A14" t="b">
         <v>0</v>
       </c>
@@ -1074,6 +1218,15 @@
       </c>
       <c r="D14" t="str">
         <v>https://hiroenglish.mykajabi.com/cushion-rentracks</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
       </c>
       <c r="H14" t="str" xml:space="preserve">
         <v xml:space="preserve"> 【案件概要】
@@ -1096,8 +1249,11 @@
 ・過去に様々な英会話学習で成果が出なかった人も多く購入している。
 ・しっかりと英会話上達を目指す方向け。</v>
       </c>
-    </row>
-    <row r="15" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -1109,6 +1265,15 @@
       </c>
       <c r="D15" t="str">
         <v>https://trial.lancul.com/stars</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
       </c>
       <c r="H15" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -1153,8 +1318,11 @@
 長期的に成果を出せるよう、訴求素材やクリエイティブのご相談も大歓迎です。
 どうぞよろしくお願いいたします。</v>
       </c>
-    </row>
-    <row r="16" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -1166,6 +1334,15 @@
       </c>
       <c r="D16" t="str">
         <v>https://g-re.bytech-ad.com/</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
       </c>
       <c r="H16" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -1211,8 +1388,11 @@
 ・その他：生成AIを触ってはいるが「作り切れない」壁を感じている方、ChatGPT等の“使う”段階から一歩先へ進みたい方
 </v>
       </c>
-    </row>
-    <row r="17" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
       <c r="A17" t="b">
         <v>0</v>
       </c>
@@ -1224,6 +1404,15 @@
       </c>
       <c r="D17" t="str">
         <v>https://eba-education.jp/btoc/lp</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
       </c>
       <c r="H17" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -1265,8 +1454,11 @@
 卒業後の就職・転職だけでなく、実際の案件獲得までサポートしてくれるスクールを探している方。
 IT人材不足という社会課題に関心があり、自身のスキルアップを通じて社会貢献も視野に入れている方。</v>
       </c>
-    </row>
-    <row r="18" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -1278,6 +1470,15 @@
       </c>
       <c r="D18" t="str">
         <v>https://up-on.jp/</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
       </c>
       <c r="H18" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
@@ -1319,68 +1520,33 @@
 経営者と話し合い、どうしたらあなたの会社の売上をあげ、改善を推進できるかを提案でき、その結果、「あなたから買いたい」と言われることにあると思います。
 もし必要な資料があれば言ってください。ご準備します。</v>
       </c>
-    </row>
-    <row r="19" ht="21" customHeight="1" xml:space="preserve">
+      <c r="I18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
       <c r="A19" t="b">
         <v>0</v>
       </c>
       <c r="B19" t="str">
-        <v>N.Y.Make-up Academy</v>
+        <v>EBAエデュケーション</v>
       </c>
       <c r="C19" t="str">
-        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.5040.7368&amp;dna=97389" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.5040.7368&amp;dna=97389" rel="nofollow noopener" target="_blank"&gt;【ニューヨークメイクアップアカデミー】&lt;/a&gt;</v>
+        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10219.15958&amp;dna=180194" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10219.15958&amp;dna=180194" rel="nofollow noopener" target="_blank"&gt;EBAエデュケーション&lt;/a&gt;</v>
       </c>
       <c r="D19" t="str">
-        <v>https://www.nyma.jp/</v>
+        <v>https://eba-education.jp/btoc/ai-jigoku/lp</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
       </c>
       <c r="H19" t="str" xml:space="preserve">
-        <v xml:space="preserve">【案件概要】
-働きながら、学校に通いながらメイクの資格を取りたい全国の皆さんへ
-自宅でメイクの取得が可能あなたの時間に合わせて学べる！
-N.Y.Make-up Academy（ニューヨークメイクアップアカデミー）資料請求
-【案件セールスポイント】
-カリキュラムにはホームスタディコース（通信）・スクーリングを組み合わせた通信・通学スタイルを用意。
-またヘアスタイリング、アイメイクスペシャリスト、ネイル、ダイヤモンドボディデザインなどの
-あなたのご希望にあわせてコースをカスタマイズ可能！
-また資料の請求、講座説明会へのご参加でメイク業界の最新情報がわかるIBF会報誌「Linque.」をもれなく全員にプレゼント！
-【案件の想定検索キーワード】
-メイク 美容 スクール 通信教育 自宅学習 美容部員 ヘアメイク
-【ターゲット層】
-男1：女9
-10代～40代のお洒落、美容、ファッション、メイクに関心のある人中心
-■掲載条件
-成果地点：新規資料請求後の入会
-成果却下条件：申込不備・重複・いたずら・不正・キャンセル
-承認サイクル：30日
-検索連動型広告出稿(リスティング)：OK
-ディスプレイ広告出稿(YDN/GDN)：OK
-Facebook集客：OK
-Twitter投稿：OK
-その他ソーシャル系集客：OK
-メールマガジン集客：OK
-ポイントサイト集客：NG
-本人申込・購入：OK
-スマートフォン最適化 ：最適化済
-広告素材/バナー ：有
-広告素材/テキスト ：有
-メルマガ素材：無
-</v>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A20" t="b">
-        <v>0</v>
-      </c>
-      <c r="B20" t="str">
-        <v>EBAエデュケーション</v>
-      </c>
-      <c r="C20" t="str">
-        <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10219.15958&amp;dna=180194" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10219.15958&amp;dna=180194" rel="nofollow noopener" target="_blank"&gt;EBAエデュケーション&lt;/a&gt;</v>
-      </c>
-      <c r="D20" t="str">
-        <v>https://eba-education.jp/btoc/ai-jigoku/lp</v>
-      </c>
-      <c r="H20" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
 EBAエデュケーションが提供する、AI×Pythonプログラミング研修の無料相談申込を募集いたします。
 本講座は、プログラミング未経験の方や、AI・Pythonをこれから学びたい社会人の方向けに、生成AIの活用、Python基礎、データ活用、Webアプリ開発などを体系的に学べるプログラミングスクールです。
@@ -1433,21 +1599,33 @@
 通年
 ※新年度前後、転職活動が活発になる時期、リスキリング需要が高まる時期、生成AI・業務効率化への関心が高まる時期は、特に訴求しやすいと考えられます。</v>
       </c>
-    </row>
-    <row r="21" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A21" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" t="str">
+      <c r="I19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" t="str">
         <v>超タイパ型 CG・VFXスクール</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C20" t="str">
         <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.11229.16043&amp;dna=180892" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.11229.16043&amp;dna=180892" rel="nofollow noopener" target="_blank"&gt;ＣＧ／ＶＦＸスクール&lt;/a&gt;</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D20" t="str">
         <v>https://school.dhw.co.jp/p/cgtpa_i/</v>
       </c>
-      <c r="H21" t="str" xml:space="preserve">
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
 デジタルハリウッド「超タイパ型 CG・VFXスクール」特設LP（https://school.dhw.co.jp/p/cgtpa_i/）への送客案件です。
 デジタルハリウッドは開校以来のべ10万人以上の卒業生をコンテンツ業界へ輩出してきた実績を持つ、30年以上の指導ノウハウを有するCG・映像専門スクールです。
@@ -1487,30 +1665,33 @@
 リスキリング・給付金制度を活用してキャリアチェンジしたい社会人
 志向：手に職をつけたい／在宅・フリーランスを含む多様な働き方を目指したい／将来的に国内外のCG業界で活躍したい層</v>
       </c>
-    </row>
-    <row r="22" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A22" t="b">
+      <c r="I20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="b">
         <v>0</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B21" t="str">
         <v>メディアエイド</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C21" t="str">
         <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.10607.15186&amp;dna=173055" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.10607.15186&amp;dna=173055" rel="nofollow noopener" target="_blank"&gt;SONOMAMA&lt;/a&gt;</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D21" t="str">
         <v>https://ma-sonomama.com/sonomama2-affi-rentracks/</v>
       </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str" xml:space="preserve">
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str" xml:space="preserve">
         <v xml:space="preserve">◆【伴走型SNSスクール】◆
 「そのままで、もっと自由に、もっと輝く。」をコンセプトに、SNSで発信したい人やSNSを仕事にしたい方をサポートするSNSオンラインスクールです。
 SNS業界トップクラスの実績を持つ株式会社メディアエイドが運営しており、累計640社以上の企業支援で培った確かなノウハウを、個人のスキルとして学べます。現役インフルエンサーによる週次でのマンツーマンサポートが強みで、受講生の個性や目標に合わせた柔軟な指導が受けられます。
@@ -1541,30 +1722,33 @@
 https://www.notion.so/mediaaid/SEO-SONOMAMA-30d86ce997bf80f0a06cc6069316432b?source=copy_link
 └ターゲットごとのインサイトやおすすめの提案方法をまとめております。</v>
       </c>
-    </row>
-    <row r="23" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" t="str">
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" t="str">
         <v>This is 英会話</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C22" t="str">
         <v>&lt;img src="https://www.rentracks.jp/adx/p.gifx?idx=0.75317.387295.6310.9068&amp;dna=114324" border="0" height="1" width="1"&gt;&lt;a href="https://www.rentracks.jp/adx/r.html?idx=0.75317.387295.6310.9068&amp;dna=114324" rel="nofollow noopener" target="_blank"&gt;【This is 英会話】&lt;/a&gt;</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D22" t="str">
         <v>https://www.thisiseikaiwa.com/</v>
       </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str" xml:space="preserve">
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str" xml:space="preserve">
         <v xml:space="preserve">【案件概要】
 京都大学教授絶賛の英語勉強法。アメリカ人約150人が登場！スマートフォンやパソコンで学べる実践的な英会話教材
 【案件セールスポイント】
@@ -1583,92 +1767,34 @@
 ・接客、道案内、観光案内などのおもてなしが必要となる場面で自信を持って会話する英会話力を身に付けたい方
 ・楽しく学びながら、英語を話す、速い英語を聴く力を伸ばしたい方</v>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A24" t="b">
-        <v>0</v>
-      </c>
-      <c r="B24" t="str">
-        <v>WACCA MUSIC SCHOOL</v>
-      </c>
-      <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FUDBUQ+5OGK+5YJRM" rel="nofollow"&gt;東京のボイトレならWACCA MUSIC SCHOOL&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC6AY+FUDBUQ+5OGK+5YJRM" alt=""&gt;</v>
-      </c>
-      <c r="D24" t="str">
-        <v>https://wacca-music.co.jp/</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str" xml:space="preserve">
-        <v xml:space="preserve">東京のボイトレスクール「WACCA MUSIC SCHOOL」です。
-銀座一丁目駅 徒歩1分、東京駅・有楽町駅から徒歩で通えるアクセスの良さと、専門性の高いジャンルが多く
-都内、関東周辺からも多くの生徒様にお通いいただいています。
-【セールスポイント】
-1.メジャーアーティスト担当講師や現役劇団四季講師がマンツーマン指導
-スターダストプロモーションに所属していた講師や、現役劇団四季講師が
-マンツーマンでレッスンを行います。
-各ジャンルの専門講師が多数所属しております。
-2.一人一人に沿ったカウンセリングを実施
-ボイトレに求めていることは人それぞれ違います。
-歌が上手くなりたい、人気者になりたい、さまざまですが、
-やりたいことを引き出し、どうやって実現するか？までを提案するため
-入会率も高く、ご好評いただいております。
-3.ジャンル数は32ジャンル
-Vtuber、KPOPボイトレ、ミュージカル、ボカロうたってみた
-イラスト、ダンス、動画編集、ミックスボイスなど
-専門的なジャンルも多数用意しておりますので
-遠方からお越しいただく生徒様も多数いらっしゃいます。
-ギターやピアノなどの楽器コースもございます。
-4.ボイトレからYoutubeの動画投稿までサポート
-歌がうまくなりたいという方から、自分のうたってみた動画を
-Youtubeにアップしてみたいという方まで幅広くサポートしています。
-5.プロになりたい方にもおすすめ
-オリジナル曲の作成から、アレンジ、MV作成までサポートしています。
-歌がうまくなるのは当たり前、作品を作り、発信するところまでをDECOでは
-大切にしています。
-【ターゲットユーザー】
-お子様から70代の方までお越しいただいておりますが
-大学生〜社会人の生徒様が多くいらっしゃいます。</v>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" t="str">
+      <c r="I22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" t="str">
         <v>Global Step Academy</v>
       </c>
-      <c r="C25" t="str" xml:space="preserve">
+      <c r="C23" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FNTK76+477W+60H7M" rel="nofollow"&gt;Global Step Academy【キャンペーン実施中】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www19.a8.net/0.gif?a8mat=4BC6AY+FNTK76+477W+60H7M" alt=""&gt;</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D23" t="str">
         <v>https://www.gsacademy.com/online</v>
       </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str" xml:space="preserve">
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 英語初心者から中・上級者まで対応する2つのコースを提供
 ・ELA Advanced:
@@ -1692,187 +1818,34 @@
 ・インターナショナルスクールの補習として利用したいご家庭
 ・英語での私立中学受験や海外留学を目指すお子様</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A26" t="b">
-        <v>0</v>
-      </c>
-      <c r="B26" t="str">
-        <v>シアーミュージック</v>
-      </c>
-      <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FJNIYQ+2UVW+614CY" rel="nofollow"&gt;マンツーマンのサックスレッスン&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www12.a8.net/0.gif?a8mat=4BC6AY+FJNIYQ+2UVW+614CY" alt=""&gt;</v>
-      </c>
-      <c r="D26" t="str">
-        <v>https://sheer.jp/sax/</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str" xml:space="preserve">
-        <v xml:space="preserve">北海道から九州まで日本全国に展開しているミュージックスクールの「シアーミュージック」。
-ボイストレーニング・ピアノ・ギター他、多くの楽器のコースをご用意してます。
-初心者の方も経験者の方も「あなたに合わせたマンツーマンレッスン」だから安心。
-WEB予約システムでいつでもどこでも携帯・パソコンから簡単にレッスンの予約をする事が
-出来るなど、通いやすい続けやすいレッスンを提供しています。
-皆様が感じたシアーミュージックの良さを
-まだ体験されていない方へぜひご紹介ください。</v>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A27" t="b">
-        <v>0</v>
-      </c>
-      <c r="B27" t="str">
-        <v>ナユタス/ダンス</v>
-      </c>
-      <c r="C27" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FKUE6A+4GDM+1BMW42" rel="nofollow"&gt;【ナユタス】上場企業グループが運営する完全マンツーマン「ダンススクール」&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www12.a8.net/0.gif?a8mat=4BC6AY+FKUE6A+4GDM+1BMW42" alt=""&gt;</v>
-      </c>
-      <c r="D27" t="str">
-        <v>https://nayutas.net/dance01/</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str" xml:space="preserve">
-        <v xml:space="preserve">◆セールスポイント◆
-・業界でも珍しい「完全マンツーマン制」を採用、
-　PV出演歴・韓国アイドル指導経験を持つプロダンサーが一対一で直接指導します。
-・HIPHOP・K-POP・ジャズ・バレエ・コンテンポラリーなど豊富なジャンルに対応し、
-　ボイトレ・楽器・動画編集コースも月謝内で複数受講が可能です。
-・目標に合わせてオーダーメイドカリキュラムを設計、
-　振替制度と無料練習スタジオ開放で無理なく続けられる環境を整えています。
-◆ターゲットユーザー◆
-・「ダンスは未経験だけど始めてみたい」という10代〜40代以上の初心者の方で、
-　グループレッスンでは恥ずかしいと感じている方。
-・K-POPやアイドルダンスに憧れる中高生・大学生・社会人で、
-　プロ水準の指導を受けてオーディションやプロデビューを目指したい方。
-・仕事や学校の都合でレッスン時間が不規則な社会人・学生で、柔軟なスケジュール対応を求めている方。
-◆おススメの提案の仕方◆
-・「マンツーマンダンスレッスン」「ダンススクール比較」などのキーワード記事で、
-　グループレッスンとの違いを訴求すると効果的です。
-・K-POPダンスや初心者ダンスに興味を持つ読者向けのSNSコンテンツや体験記事で、
-　50分の無料体験レッスンの充実度を紹介する方法がおすすめです。
-・「習い事を探している」「大人になってからダンスを始めたい」といった悩み解決型の記事から、
-　全国70校以上の通いやすさを合わせてアピールしてください。</v>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A28" t="b">
-        <v>0</v>
-      </c>
-      <c r="B28" t="str">
-        <v>ナユタス/ボイトレ</v>
-      </c>
-      <c r="C28" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FIGNR6+4GDM+C0YF6" rel="nofollow"&gt;自由テキスト1&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC6AY+FIGNR6+4GDM+C0YF6" alt=""&gt;</v>
-      </c>
-      <c r="D28" t="str">
-        <v>https://nayutas.net/lp01/</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str" xml:space="preserve">
-        <v xml:space="preserve">【ナユタス】上場企業グループが運営する「ボイトレ・ダンススクール」
-◆セールスポイント◆
-生徒さんの満足度95％！
-体験レッスン後の入校が80%以上と抜群の入校率！
-ボイストレーニング・マンツーマンダンスならNAYUTAS（ナユタス）
-新宿・渋谷・船橋・名古屋・梅田・福岡など全国43校で展開するボイストレーニングとマンツーマンダンスが同
-時に習える複合型エンタメスクールNAYUTAS（ナユタス）。
-あなたに合わせた、あなただけのレッスンで、個性を引き出すNAYUTASでは、
-カウンセリングを行いあなたが抱える問題や悩みや目的などを明確化し、
-一人ひとりに合うあなただけのカリキュラムを作ることで、内容の濃いレッスンに取り組めます。
-さらに、選び抜かれたプロの担当講師が、あなたが持つ個性を的確に活かします。
-Point 01
-個人レッスン
-完全マンツーマンのレッスンなので、
-あなたが抱える問題や悩みや目的などを明確化し、一人ひとりに合わせたレッスンができます。
-Point 02
-安心のレッスン振替制度
-お仕事や学校が忙しい方でも安心。
-固定のレッスン日が都合悪くなってしまった場合も、後日無料で振替のレッスンを受けられます。
-Point 03
-レコーディングが無料！
-オーディションやボイスサンプル用の素材が必要な方、
-CDや音源データなどで自分の作品を形にしてみたい方も無料でプロクオリティーのレコーディングができます。
-Point 04
-経験豊富なプロ講師
-講師としての経験はもちろん、音楽活動の経験豊富な講師陣がそろっています。
-あなたが「やりたい」と思ったことを徹底的にサポートします。
-Point 05
-日本最大の韓国語教室 K Village Tokyo が運営。
-ナユタスは 日本最大の韓国語教室 K Village Tokyo が運営。
-K-POPアイドルを目指すコースも充実！
-Point 06
-ボイトレ・マンツーマンダンスどちらも習える！
-月額の月謝内でカリキュラムをカスタマイズできるので歌って踊れるダンサーも目指せます。
-◆ターゲットユーザー◆
-【女性】
-10代・20代・30代・40代・50代・60代以上・全世代
-【男性】
-10代・20代・30代・40代・50代・60代以上・全世代</v>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A29" t="b">
-        <v>1</v>
-      </c>
-      <c r="B29" t="str">
+      <c r="I23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" t="str">
         <v>能セン</v>
       </c>
-      <c r="C29" t="str" xml:space="preserve">
+      <c r="C24" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FH9SJM+5TS8+5YJRM" rel="nofollow"&gt;資格合格支援スクール【能セン】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www14.a8.net/0.gif?a8mat=4BC6AY+FH9SJM+5TS8+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D24" t="str">
         <v>https://www.nouryoku.com/</v>
       </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str" xml:space="preserve">
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str" xml:space="preserve">
         <v xml:space="preserve">能センは、電験三種や1・2級施工管理技士など需要の高い国家資格に特化した学習スクールです。
 オンラインと通学の両方に対応しており、忙しい社会人でも学習を続けやすい環境が整っています。
 最大の強みは、受講生の学習状況を毎日フォローする「勉強フォローアップサービス」です。
@@ -1894,34 +1867,34 @@
 ・「続かない」「やり方が分からない」という悩みに寄り添った訴求が効果的
 ・講師サポートの充実度や教材の分かりやすさを安心材料として提示</v>
       </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A30" t="b">
-        <v>1</v>
-      </c>
-      <c r="B30" t="str">
+      <c r="I24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" t="str">
         <v>アバロンミュージックスクール</v>
       </c>
-      <c r="C30" t="str" xml:space="preserve">
+      <c r="C25" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FBWW3M+4FRO+5YRHE" rel="nofollow"&gt;「音楽プロデューサー」が設立【アバロンミュージックスクール】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www13.a8.net/0.gif?a8mat=4BC6AY+FBWW3M+4FRO+5YRHE" alt=""&gt;</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D25" t="str">
         <v>https://www.avalon-works.com/</v>
       </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str" xml:space="preserve">
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str" xml:space="preserve">
         <v xml:space="preserve">Amazon音楽書部門で1位を獲得
 Amazon新着音楽メソドランキング1位を獲得した、
 アバロン公式ボイトレ本「スマホで簡単レッスン究極のボイトレ」。
@@ -1946,34 +1919,34 @@
 歌だけでなく、声優や話し方のボイトレレッスンもあり、非常に好評です。
 中高生、60歳以上の方は全コースが割引適用で毎月レッスン料が10%OFF！</v>
       </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A31" t="b">
-        <v>1</v>
-      </c>
-      <c r="B31" t="str">
+      <c r="I25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" t="str">
         <v>住宅デザイン研究所</v>
       </c>
-      <c r="C31" t="str" xml:space="preserve">
+      <c r="C26" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FAQ0W2+4O48+60H7M" rel="nofollow"&gt;ハウジングインテリアカレッジの通信講座&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC6AY+FAQ0W2+4O48+60H7M" alt=""&gt;</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D26" t="str">
         <v>https://www.jdknet.co.jp/</v>
       </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str" xml:space="preserve">
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 当スクールはインテリアコーディネーター通信講座を37年間、
 二球建築士通信講座を20年間行っているスクールです。
@@ -1997,80 +1970,34 @@
 またどこにも負けない丁寧な添削で合格をぐっと引き寄せます。
 添削数の多さと価格の安さはどこにも負けません。</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A32" t="b">
-        <v>0</v>
-      </c>
-      <c r="B32" t="str">
-        <v>資格スクール特集</v>
-      </c>
-      <c r="C32" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FA4LAA+22BU+NTJWY" rel="nofollow"&gt;資格スクール特集&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www18.a8.net/0.gif?a8mat=4BC6AY+FA4LAA+22BU+NTJWY" alt=""&gt;</v>
-      </c>
-      <c r="D32" t="str">
-        <v>https://naruniwa.tv/lp/campaign/ad/tsugakukouza/</v>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str" xml:space="preserve">
-        <v xml:space="preserve">特徴１．
-専門学校・スクールの学校パンフレットが「無料」で「カンタン資料請求」ができます！
-・専門学校は、高校生はもちろん、最近では大学生や若い社会人の再進学も増えてきています。
-特に資格が取得できる専門学校は社会人の方にも選ばれています。
-・スクールは趣味で習うだけでなく、資格を取って就職を目指せるスクールのみ掲載しています。
-特徴２．
-LINEで進路相談を受け付けています！
-資料請求した方に向けて「進路相談LINE」のURLをお送りしております。
-進路相談LINEでは、進学の悩みや疑問、学校選びの方法などをロボット（bot）とオペレーター（人）の二通りで対応しています。
-利用については無料です！
-友達数は2500名を突破！今も増え続けています。
-こんな人にピッタリ↓↓
-・なんとなくやりたいことは決まっているけれど、学校が分からない
-・進路に悩んでいる。やりたいことがみつからない。
-・社会人（大学生）だけど、もう一度勉強し直したい。
-まずはなるにはサイトで資料請求。そして、LINEで進路相談してみて下さい。
-進路の方向が見えるかもしれませんよ！</v>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A33" t="b">
-        <v>1</v>
-      </c>
-      <c r="B33" t="str">
+      <c r="I26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" t="str">
         <v>SkillHacks</v>
       </c>
-      <c r="C33" t="str" xml:space="preserve">
+      <c r="C27" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+DGMWQQ+4K3S+5YJRM" rel="nofollow"&gt;SkillHacks(スキルハックス) &lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC6AY+DGMWQQ+4K3S+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D27" t="str">
         <v>https://brain-holdings.com/skillhacks/</v>
       </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
-      <c r="H33" t="str" xml:space="preserve">
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str" xml:space="preserve">
         <v xml:space="preserve">■サービス/商品の概要
 SkillHacks(スキルハックス)は、Webアプリケーション開発を学べるオンラインプログラミングスクールです。
 MovieHacks（ムービーハックス）は動画編集を学べるオンライン動画編集スクールです。
@@ -2089,34 +2016,34 @@
 ・SkillHacks、スキルハックス、MovieHacks、ムービーハックス、
   迫佑樹などの商標リスティングおよび個人名での部分一致を含むリスティングはNGとなっております。</v>
       </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A34" t="b">
-        <v>1</v>
-      </c>
-      <c r="B34" t="str">
+      <c r="I27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" t="str">
         <v>ヴィノテラス ワインスクール</v>
       </c>
-      <c r="C34" t="str" xml:space="preserve">
+      <c r="C28" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+DE96BM+4X0S+5YJRM" rel="nofollow"&gt;ヴィノテラス ワインスクール&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC6AY+DE96BM+4X0S+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D28" t="str">
         <v>https://school.vnts.jp/</v>
       </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
-      <c r="H34" t="str" xml:space="preserve">
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 ヴィノテラス ワインスクールはオンラインに特化したワインスクールなので、
 スクールに通学せず、好きな場所で受講いただけます。
@@ -2137,80 +2064,34 @@
 取り上げてほしい講座などアンケート項目もございますので、
 いつか貴方の希望の講座が現実のものになるかもです！</v>
       </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A35" t="b">
-        <v>0</v>
-      </c>
-      <c r="B35" t="str">
-        <v>fan.salon</v>
-      </c>
-      <c r="C35" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FYJD36+5FAU+5YJRM" rel="nofollow"&gt;LINEでオンランサロン【fan.salon】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www12.a8.net/0.gif?a8mat=4BC6AY+FYJD36+5FAU+5YJRM" alt=""&gt;</v>
-      </c>
-      <c r="D35" t="str">
-        <v>https://www.fan.salon/</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35" t="str" xml:space="preserve">
-        <v xml:space="preserve">◆セールスポイント◆
-fan.salonは、LINEを活用して独自のオンラインサロンを簡単に開設・運営できるサービスです。
-インフルエンサー、クリエイター、教育者、専門家、または小規模ビジネスオーナーなど、多くのフォロワーや
-ファンを抱える方々にとって新たな収入源を創ることができます。
-LINEの使い勝手の良さを生かし、ファン専用の動画コンテンツやライブ配信、イベントの告知、ショッピング、
-チャットなど、様々な機能を活用して、ファンにより満足してもらえるサービスを提供することが可能です。
-◆ターゲット◆
-・ファン限定動画コンテンツ、ライブの配信をしたい方
-・ファン限定ブログや写真の配信をしたい方
-・ファン限定グッズなど商品販売をしたい方
-・ファン同士の交流の場を提供したい方
-・その他会員限定サービスを構築したい方　など
-◆おすすめの提案の仕方◆
-会員限定という切り口であれば本サービスの活用方法は無限に存在いたします。
-弊社でも既に存在する会員制ビジネスをヒントにした提案は効果が非常に高いです。
-ご自身の得意ジャンルの会員制ビジネスのご提案をしていただくことがおすすめです。
-</v>
-      </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A36" t="b">
-        <v>1</v>
-      </c>
-      <c r="B36" t="str">
+      <c r="I28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" t="str">
         <v>WEBCOACH</v>
       </c>
-      <c r="C36" t="str" xml:space="preserve">
+      <c r="C29" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC3YO+EHJRH6+5EVK+5YJRM" rel="nofollow"&gt;WEBCOACH｜副業・フリーランス特化型のオンラインWebデザインスクール&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www18.a8.net/0.gif?a8mat=4BC3YO+EHJRH6+5EVK+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D29" t="str">
         <v>https://www.webcoach.jp/a8/</v>
       </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-      <c r="F36" t="str">
-        <v/>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
-      <c r="H36" t="str" xml:space="preserve">
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
         <v xml:space="preserve">＜オンラインWebデザインスクール『WEBCOACH』の案件＞
 ★ ターゲットと商材
 ターゲットは、副業・フリーランスを目指す（主に）女性の方で年齢が20代 - 40代の方となります。
@@ -2234,34 +2115,34 @@
 さらに、分割払い制度を利用することで最低で9,800円まで月々の支払いを抑えることも可能となっております。
 </v>
       </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A37" t="b">
-        <v>1</v>
-      </c>
-      <c r="B37" t="str">
+      <c r="I29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" t="str">
         <v>Wannabeアカデミー</v>
       </c>
-      <c r="C37" t="str" xml:space="preserve">
+      <c r="C30" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+G995Z6+4NJO+5YJRM" rel="nofollow"&gt;未経験者に対して3か月でwebマーケターに育てます【Wannabeアカデミー】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC6AY+G995Z6+4NJO+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D37" t="str">
+      <c r="D30" t="str">
         <v>https://shareway.jp/wannabe_web/2-main/</v>
       </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37" t="str" xml:space="preserve">
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 Webマーケティング実務特化型のカリキュラム
 Webマーケティング学習に重要なのは『実務経験』です。
@@ -2290,34 +2171,34 @@
 　期間内は何度でも学び直しができます。
 ６．追加料金なしで最大8ヶ月+無期限のキャリア(転職・副業)サポート</v>
       </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A38" t="b">
-        <v>1</v>
-      </c>
-      <c r="B38" t="str">
+      <c r="I30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" t="str">
         <v>ショーバ中国語センター</v>
       </c>
-      <c r="C38" t="str" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+GFSXMQ+5WP8+5YJRM" rel="nofollow"&gt;発音矯正×会話力を同時育成！プロ講師のWebレッスン【ショーバ中国語センター】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www14.a8.net/0.gif?a8mat=4BC6AY+GFSXMQ+5WP8+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D31" t="str">
         <v>https://www.shuoba.jp/weblesson/</v>
       </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-      <c r="F38" t="str">
-        <v/>
-      </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
-      <c r="H38" t="str" xml:space="preserve">
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 ・日本人教育経験が豊富なプロ講師が発音矯正と会話力を同時に育成します。
 ・独自Webアプリは自動録画機能・マウス書き込み機能を搭載し、臨場感ある授業と効率的な復習を実現します。
@@ -2332,34 +2213,34 @@
 ・「中国赴任前に備えておきたい語学学習法」など赴任準備をテーマにした記事での訴求もおすすめです。
 ・スカイプレッスンや独学との違いを比較し、録画機能・発音矯正などの差別化ポイントを伝える記事も成果に繋がりやすいです</v>
       </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A39" t="b">
-        <v>1</v>
-      </c>
-      <c r="B39" t="str">
+      <c r="I31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" t="str">
         <v>英論会</v>
       </c>
-      <c r="C39" t="str" xml:space="preserve">
+      <c r="C32" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AZ+3KNYA+4NPS+BWVTE" rel="nofollow"&gt;合格保証制度あり！【英論会】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC6AZ+3KNYA+4NPS+BWVTE" alt=""&gt;</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D32" t="str">
         <v>https://www.eiken-passport.com/</v>
       </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
-      <c r="H39" t="str" xml:space="preserve">
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 合格保証つき英検指導専門塾、オンライン塾、英語が苦手な生徒におすすめの塾、
 中高一貫校の生徒におすすめの塾、
@@ -2383,34 +2264,34 @@
 など、記事の中でおすすめとして紹介していただけますと幸いでございます。
 </v>
       </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A40" t="b">
+      <c r="I32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="b">
         <v>0</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B33" t="str">
         <v>現代日本国語塾</v>
       </c>
-      <c r="C40" t="str" xml:space="preserve">
+      <c r="C33" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AZ+463K2+4NPS+HVFKY" rel="nofollow"&gt;国語専門のプロ講師がオンラインでマンツーマン指導！【現代日本国語塾】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC6AZ+463K2+4NPS+HVFKY" alt=""&gt;</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D33" t="str">
         <v>https://sukyojuku.com/</v>
       </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str" xml:space="preserve">
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 国語専門塾、オンライン塾、国語が苦手な生徒におすすめの塾、中高一貫校の生徒におすすめの塾、
 インターナショナルスクールに対応している塾！といった記事で
@@ -2434,34 +2315,34 @@
 など、記事の中でおすすめとして紹介していただけますと幸いでございます。
 </v>
       </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A41" t="b">
-        <v>1</v>
-      </c>
-      <c r="B41" t="str">
+      <c r="I33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" t="str">
         <v>数強塾</v>
       </c>
-      <c r="C41" t="str" xml:space="preserve">
+      <c r="C34" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AZ+2Z8CI+4NPS+5YRHE" rel="nofollow"&gt;「数強塾」オンライン数学克服塾〈プロ講師〉&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www13.a8.net/0.gif?a8mat=4BC6AZ+2Z8CI+4NPS+5YRHE" alt=""&gt;</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D34" t="str">
         <v>https://sukyojuku.com/</v>
       </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str" xml:space="preserve">
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str" xml:space="preserve">
         <v xml:space="preserve"> 
 ◆セールスポイント◆
 数学専門塾、オンライン塾、数学が苦手な生徒におすすめの塾、中高一貫校の生徒におすすめの塾、
@@ -2492,34 +2373,34 @@
 など、記事の中でおすすめとして紹介していただけますと幸いでございます。
 </v>
       </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A42" t="b">
-        <v>1</v>
-      </c>
-      <c r="B42" t="str">
+      <c r="I34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" t="str">
         <v>アカデミー・デュ・ヴァン</v>
       </c>
-      <c r="C42" t="str" xml:space="preserve">
+      <c r="C35" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AZ+1SD4Y+4EDY+61RIA" rel="nofollow"&gt;ワインを学ぶなら国内No.1の【アカデミー・デュ・ヴァン】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC6AZ+1SD4Y+4EDY+61RIA" alt=""&gt;</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D35" t="str">
         <v>https://www.adv.gr.jp/</v>
       </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-      <c r="H42" t="str" xml:space="preserve">
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 アカデミー・デュ・ヴァンは、パリ発祥、30年以上の歴史を誇る日本最大のワインスクール。
 東京（青山校、銀座校）、大阪、名古屋に在り、
@@ -2540,34 +2421,34 @@
 海外旅行が好きな方。
 飲食・サービス業に関わる方。</v>
       </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A43" t="b">
-        <v>1</v>
-      </c>
-      <c r="B43" t="str">
+      <c r="I35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" t="str">
         <v>SARAスクール</v>
       </c>
-      <c r="C43" t="str" xml:space="preserve">
+      <c r="C36" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+GI6O1U+4N6C+7925E" rel="nofollow"&gt;リンパケアセラピスト資格を簡単に取得できる人気の通信講座【SARAスクール】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC6AY+GI6O1U+4N6C+7925E" alt=""&gt;</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D36" t="str">
         <v>https://www.saraschool.net/biyo/lymphcare/</v>
       </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str" xml:space="preserve">
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 ・受講卒業するだけで資格を取得できます。
 ・女性のための通信講座
@@ -2582,141 +2463,34 @@
 ・講座数は290講座以上
 ・初心者でも簡単に資格取得できます。</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A44" t="b">
+      <c r="I36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="b">
         <v>0</v>
       </c>
-      <c r="B44" t="str">
-        <v>一般社団法人和文化推進協会</v>
-      </c>
-      <c r="C44" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+GIS3NM+4V0U+ZQFQA" rel="nofollow"&gt;【動画教材エディター養成コース】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www18.a8.net/0.gif?a8mat=4BC6AY+GIS3NM+4V0U+ZQFQA" alt=""&gt;</v>
-      </c>
-      <c r="D44" t="str">
-        <v>https://school.suzaku.or.jp/p/editor-training</v>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str" xml:space="preserve">
-        <v xml:space="preserve">◆セールスページのシステムが、ページ訪問者への自動クロージング（申込訴求）を行います。◆
-・ページ訪問者に対して、それぞれの訪問タイミングから計測して、
-　各個別に48時間のカウントダウンが発動します。
-・このカウントダウン期間中のみ50%OFF割引キャンペーンが行われる、
-　期間限定の自動クロージングシステムとなっています。
-◆わかりやすい説明動画があります◆
-3分29秒の動画でわかりやすく説明しています → https://link.suzaku.or.jp/vimeo-a8
-◆セールスポイント◆
-1・期間限定の割引価格で受講できます。定価199,800円 → 99,800円               
-2・これまで他にはない日本初のオリジナル講座です。
-3・単独講師ではなく、それぞれのジャンル実績者3名のプロ講師によるカリキュラムです。
-4・動画教材+グループセッション+コミュニティ+OJT（実地研修）による充実の内容となっています。
-5・養成コース修了後、資格認定があります。
-6・資格取得者には見込客をご紹介します。
-7・見込客からは固定報酬+歩合報酬で業務受注が見込めます。
-8・スクール運営者が協会（非営利団体）である為、公的安心感もPRに活用できます。
-◆ターゲットユーザー◆
-・動画編集業務を仕事としている方
-・動画編集の仕事に経験がある方
-・動画編集を趣味として行なっている方
-・動画の仕事で稼ぎたい方</v>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A45" t="b">
-        <v>0</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Voice Camp</v>
-      </c>
-      <c r="C45" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+GEM2F6+5T74+5YJRM" rel="nofollow"&gt;業界最安値！完全オンラインのマンツーマンボイススクール【Voice Camp（ボイスキャンプ）】&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www17.a8.net/0.gif?a8mat=4BC6AY+GEM2F6+5T74+5YJRM" alt=""&gt;</v>
-      </c>
-      <c r="D45" t="str">
-        <v>https://voicecamp.jp/</v>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v/>
-      </c>
-      <c r="H45" t="str" xml:space="preserve">
-        <v xml:space="preserve">「Voice Camp」は、声優に関するスキルを習得できる完全オンラインのマンツーマンボイススクールです！
-初心者からプロを目指す方まで、幅広いレベルに対応したレッスンを提供しており、
-声の表現力を高めるための実践的なカリキュラムが特徴です！
-■ターゲットユーザー
-・声優やナレーターを目指している方
-・声を使った仕事に興味があるけれど、何から始めればよいか分からない方
-・短期間で自分の声の使い方を向上させたい方
-・オンラインで手軽に音声のスキルを学びたい方
-■Voice Campが選ばれる6つの理由
-1.低価格で気軽にスタート
-養成所や専門学校とは異なり、お手頃な価格でレッスンを受けられます。
-月2回12,100円（税込）から始められるので、高額な初期費用を気にする必要がございません。
-2.経験豊富なプロ講師陣
-専門学校、養成所、大手声優事務所を経て、アニメやナレーションなど
-様々な現場を経験した講師陣が全力でサポートします。
-3.完全マンツーマンで50分レッスン
-一般的な養成所では一人当たりの指導時間はわずか6分程度です。
-当スクールでは50分間、プロの指導を独り占めできるため、短期間で効率よくスキルアップが可能です。
-4.場所を問わないオンラインレッスン
-必要なのはPCまたはスマホ1台と、声を出せる環境だけ。
-インターネットさえあれば、自宅など好きな場所でレッスンを受けられます。
-5.無料体験レッスン実施中
-今なら1レッスン3,000円が無料で受けられます。
-プロの講師が学習目的や目標を丁寧にヒアリングし、最適な学習方法を提案します。
-6.都合に合わせて自由に振替可能
-レッスン前日までの連絡で、キャンセル料はかかりません。
-急な予定が入っても、生徒の都合に合わせて好きなタイミングで受講ができます。
-</v>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A46" t="b">
-        <v>0</v>
-      </c>
-      <c r="B46" t="str">
+      <c r="B37" t="str">
         <v>LECオンライン</v>
       </c>
-      <c r="C46" t="str" xml:space="preserve">
+      <c r="C37" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+GB1GSI+1G62+6BMG2" rel="nofollow"&gt;行政書士サイトはこちら&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www19.a8.net/0.gif?a8mat=4BC6AY+GB1GSI+1G62+6BMG2" alt=""&gt;</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D37" t="str">
         <v>https://www.lec-jp.com/gyousei/</v>
       </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46" t="str">
-        <v/>
-      </c>
-      <c r="H46" t="str" xml:space="preserve">
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
         <v xml:space="preserve">LEC東京リーガルマインドは、資格受験指導37年の実績とノウハウを持ち、
 司法試験、司法書士、弁理士をはじめとする
 各種国家資格および検定受験の対策講座を全国展開する資格取得・通信教育のスクールです。
@@ -2725,84 +2499,34 @@
 また、インターネットによるWeb通信講座、音声ダウンロード講座、スマートフォン講座など学習スタイルが多彩で、
 話題性の高い学習教材が常に注目を集めています。</v>
       </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A47" t="b">
-        <v>0</v>
-      </c>
-      <c r="B47" t="str">
-        <v>介護美容研究所</v>
-      </c>
-      <c r="C47" t="str" xml:space="preserve">
-        <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FZQ8AQ+4LBY+BWVTE" rel="nofollow"&gt;介護美容研究所・訪問美容コース&lt;/a&gt;
-&lt;img border="0" width="1" height="1" src="https://www10.a8.net/0.gif?a8mat=4BC6AY+FZQ8AQ+4LBY+BWVTE" alt=""&gt;</v>
-      </c>
-      <c r="D47" t="str">
-        <v>https://academybc.jp/lpa/</v>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47" t="str">
-        <v/>
-      </c>
-      <c r="H47" t="str" xml:space="preserve">
-        <v xml:space="preserve">■介護美容研究所とは
-「高齢者に美容を届ける」技術に特化した社会人向けのプロスクールです
-◆スクールの目的■
-1. 2025年には人口の3割が65歳以上となる
-2. 美容を気にせず人前に出る(すっぴん等)ことが恥ずかしいという世代が
-　高齢になり自分で美容を行うことが困難になってきている
-3. 現在の介護保険制度は保険内で美容を提供する仕様となっていない
-上記の様な状況の中、いくら店舗でお客様を待っていても、高齢者施設の利用者や寝たきりの方などは美容室へ
-来店することができません。
-訪問美容とは、そうしたお客様の元へ美容師自らが訪問し、美容サービスを提供するお仕事です。
-◆セールスポイント◆
-　・訪問美容師と介護施設を繋げるマッチングサービスを利用して、他社にはないサポートで訪問美容を始める
-ことができます。
-　・寝たきりの方へのカット術や、施設・居宅での施術フローなどを学ぶことができます。
-　・訪問美容ワークに特化した介護資格を取得でき、介護施設に求められる訪問美容師になれます。
-　・「介護の知識や技術」があり、「対高齢者に特化した美容ノウハウ」を持った、質の高い訪問美容サービス
-を提供できる人材になれます。
-　・感染症専門医監修による、受講環境の整備と現場での感染症対策を盛り込んだカリキュラムを提供します
-　・経済産業省より採択を受け、美容・介護両業界団体から参画いただき「訪問理美容協議会」
-　　を設立。　主幹事として、訪問理美容の衛生管理・必要技術に関するガイドラインである、
-　 「訪問理美容サービス提供事業者に対するガイドライン」 を策定しました。</v>
-      </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A48" t="b">
-        <v>1</v>
-      </c>
-      <c r="B48" t="str">
+      <c r="I37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" t="str">
         <v>行政書士TEPPAN通信講座</v>
       </c>
-      <c r="C48" t="str" xml:space="preserve">
+      <c r="C38" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FZ4SOY+408S+HV7V6" rel="nofollow"&gt;"鉄板"教材で効率よく学ぶ！【行政書士TEPPAN通信講座】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www14.a8.net/0.gif?a8mat=4BC6AY+FZ4SOY+408S+HV7V6" alt=""&gt;</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D38" t="str">
         <v>https://onsuku.jp/dlc/gyousei</v>
       </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48" t="str">
-        <v/>
-      </c>
-      <c r="H48" t="str" xml:space="preserve">
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 ・行政書士試験の重要論点に絞って学べる、書籍＋オンライン講義の通信講座
 ・「スッキリわかる行政書士」シリーズと連動した講義で、初学者でも理解しやすい構成
@@ -2824,34 +2548,34 @@
 ・問題演習・過去問を含む実践的な内容であることを伝える
 </v>
       </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A49" t="b">
-        <v>1</v>
-      </c>
-      <c r="B49" t="str">
+      <c r="I38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" t="str">
         <v>ハッチリンク ジュニア</v>
       </c>
-      <c r="C49" t="str" xml:space="preserve">
+      <c r="C39" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FVK72A+3O9E+5YJRM" rel="nofollow"&gt;ハッチリンクジュニア&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www14.a8.net/0.gif?a8mat=4BC6AY+FVK72A+3O9E+5YJRM" alt=""&gt;</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D39" t="str">
         <v>https://www.hatchlinkjr.com/</v>
       </c>
-      <c r="E49" t="str">
-        <v/>
-      </c>
-      <c r="F49" t="str">
-        <v/>
-      </c>
-      <c r="G49" t="str">
-        <v/>
-      </c>
-      <c r="H49" t="str" xml:space="preserve">
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str" xml:space="preserve">
         <v xml:space="preserve">◆セールスポイント◆
 【ハッチリンクジュニア】は
 満足度96%以上の子供専用、オンライン英会話スクールです。
@@ -2870,34 +2594,34 @@
 小学校高学年、中学生、高校生のお子様へは、
 英検対策や教育指導要領にそった英語教材で効率的に英会話を学習できます。</v>
       </c>
-      <c r="I49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="21" customHeight="1" xml:space="preserve">
-      <c r="A50" t="b">
-        <v>1</v>
-      </c>
-      <c r="B50" t="str">
+      <c r="I39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" t="str">
         <v>オンスク.JP</v>
       </c>
-      <c r="C50" t="str" xml:space="preserve">
+      <c r="C40" t="str" xml:space="preserve">
         <v xml:space="preserve">&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC6AY+FXCHVM+408S+60WN6" rel="nofollow"&gt;月額定額サービス【ウケホーダイ】&lt;/a&gt;
 &lt;img border="0" width="1" height="1" src="https://www19.a8.net/0.gif?a8mat=4BC6AY+FXCHVM+408S+60WN6" alt=""&gt;</v>
       </c>
-      <c r="D50" t="str">
+      <c r="D40" t="str">
         <v>https://onsuku.jp/</v>
       </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
-      <c r="F50" t="str">
-        <v/>
-      </c>
-      <c r="G50" t="str">
-        <v/>
-      </c>
-      <c r="H50" t="str" xml:space="preserve">
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str" xml:space="preserve">
         <v xml:space="preserve">……━━…━━…━━…━…━━━━━━━━━━━━━━━━━━━━
 様々な資格学習が1628円でウケホーダイ！
 いつでもどこでも勉強できるオンラインの資格学習サービス
@@ -2937,11 +2661,301 @@
 ・低料金で資格取得をしたい方
 </v>
       </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="b">
+        <v>0</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="b">
+        <v>0</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="b">
+        <v>0</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="b">
+        <v>0</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="b">
+        <v>0</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="b">
+        <v>0</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="b">
+        <v>0</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="b">
+        <v>0</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="b">
+        <v>0</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="b">
+        <v>0</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
       <c r="I50" t="str">
         <v/>
       </c>
     </row>
-    <row r="51" ht="21" customHeight="1">
+    <row r="51">
       <c r="A51" t="b">
         <v>0</v>
       </c>
@@ -2970,300 +2984,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="A52" t="b">
-        <v>0</v>
-      </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-      <c r="I52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="21" customHeight="1">
-      <c r="A53" t="b">
-        <v>0</v>
-      </c>
-      <c r="B53" t="str">
-        <v/>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
-        <v/>
-      </c>
-      <c r="H53" t="str">
-        <v/>
-      </c>
-      <c r="I53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" t="b">
-        <v>0</v>
-      </c>
-      <c r="B54" t="str">
-        <v/>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54" t="str">
-        <v/>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
-      <c r="I54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="21" customHeight="1">
-      <c r="A55" t="b">
-        <v>0</v>
-      </c>
-      <c r="B55" t="str">
-        <v/>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-      <c r="E55" t="str">
-        <v/>
-      </c>
-      <c r="F55" t="str">
-        <v/>
-      </c>
-      <c r="G55" t="str">
-        <v/>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
-      <c r="I55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" t="b">
-        <v>0</v>
-      </c>
-      <c r="B56" t="str">
-        <v/>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v/>
-      </c>
-      <c r="E56" t="str">
-        <v/>
-      </c>
-      <c r="F56" t="str">
-        <v/>
-      </c>
-      <c r="G56" t="str">
-        <v/>
-      </c>
-      <c r="H56" t="str">
-        <v/>
-      </c>
-      <c r="I56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="21" customHeight="1">
-      <c r="A57" t="b">
-        <v>0</v>
-      </c>
-      <c r="B57" t="str">
-        <v/>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-      <c r="E57" t="str">
-        <v/>
-      </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="21" customHeight="1">
-      <c r="A58" t="b">
-        <v>0</v>
-      </c>
-      <c r="B58" t="str">
-        <v/>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
-        <v/>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="21" customHeight="1">
-      <c r="A59" t="b">
-        <v>0</v>
-      </c>
-      <c r="B59" t="str">
-        <v/>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="21" customHeight="1">
-      <c r="A60" t="b">
-        <v>0</v>
-      </c>
-      <c r="B60" t="str">
-        <v/>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v/>
-      </c>
-      <c r="G60" t="str">
-        <v/>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="A61" t="b">
-        <v>0</v>
-      </c>
-      <c r="B61" t="str">
-        <v/>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
-        <v/>
-      </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I51"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_スキルアップ図鑑.xlsx
@@ -126,10 +126,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -161,10 +161,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2993,7 +2993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="22.8333333333333"/>
     <col min="2" max="2" customWidth="1" width="84.8333333333333"/>
@@ -3100,23 +3100,23 @@
         <v/>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>取り込みを実行すると、この欄に「[自動] 日付 …」の1行が追記され、</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ジャンルの一覧</v>
+        <v/>
       </c>
       <c r="B14" t="str">
-        <v>プログラミング・エンジニア、Webデザイン、UI/UXデザイン、動画編集、Webマーケティング、生成AI・DXリテラシー、語学、資格</v>
+        <v>掲載できたか・できなかった場合はその理由が残ります。</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>受講スタイルの一覧</v>
+        <v/>
       </c>
       <c r="B15" t="str">
-        <v>オンライン、通学、オンライン・通学の併用可</v>
+        <v>ご自身で書いた内容は消えません（[自動] の行だけが毎回書き換わります）。</v>
       </c>
     </row>
     <row r="16">
@@ -3129,18 +3129,18 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>注意</v>
+        <v>ジャンルの一覧</v>
       </c>
       <c r="B17" t="str">
-        <v>このシートに書いた紹介文が、そのままサイトに掲載されることはありません。</v>
+        <v>プログラミング・エンジニア、Webデザイン、UI/UXデザイン、動画編集、Webマーケティング、生成AI・DXリテラシー、語学、資格</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>受講スタイルの一覧</v>
       </c>
       <c r="B18" t="str">
-        <v>料金・特徴などは公式サイトの記載を機械的に確認したうえで掲載します。</v>
+        <v>オンライン、通学、オンライン・通学の併用可</v>
       </c>
     </row>
     <row r="19">
@@ -3148,13 +3148,36 @@
         <v/>
       </c>
       <c r="B19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>注意</v>
+      </c>
+      <c r="B20" t="str">
+        <v>このシートに書いた紹介文が、そのままサイトに掲載されることはありません。</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v>料金・特徴などは公式サイトの記載を機械的に確認したうえで掲載します。</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="B22" t="str">
         <v>確認できなかった項目は「要問い合わせ」と表示されます。</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B22"/>
   </ignoredErrors>
 </worksheet>
 </file>